--- a/Project Requirements Form (Excel).xlsx
+++ b/Project Requirements Form (Excel).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swilli06\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parke\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30401BB4-BD22-43D4-9616-5D465FBC0724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2E9DFFC-821E-4C6E-827A-C75BB8035C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Requirements" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="127">
   <si>
     <t>CSCE 40003 Software Engineering</t>
   </si>
@@ -383,6 +383,30 @@
   </si>
   <si>
     <t>Easy to navigate, looks nice, usable, helpful</t>
+  </si>
+  <si>
+    <t>easy useage and works</t>
+  </si>
+  <si>
+    <t>easy for user to update, looks nice</t>
+  </si>
+  <si>
+    <t>functional</t>
+  </si>
+  <si>
+    <t>clear cut and fully transparent</t>
+  </si>
+  <si>
+    <t>visible area and acurate</t>
+  </si>
+  <si>
+    <t>functional and accurate</t>
+  </si>
+  <si>
+    <t>real time, functional</t>
+  </si>
+  <si>
+    <t>accurate forcasting</t>
   </si>
 </sst>
 </file>
@@ -517,31 +541,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -552,12 +560,26 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="AM Cell Style - Orange" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
@@ -833,1792 +855,972 @@
   <dimension ref="A1:J201"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="38" style="7" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="49.7109375" style="7" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="38" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="49.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
+      <c r="A3" s="3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="12">
         <v>45897</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="A6" s="3"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="A7" s="3"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+      <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+      <c r="A11" s="1">
         <v>2</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="14"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
+      <c r="A12" s="1">
         <v>3</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="14"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
+      <c r="A13" s="1">
         <v>4</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H13" s="14"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
+      <c r="A14" s="1">
         <v>5</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
+      <c r="A15" s="1">
         <v>6</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="14"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
+      <c r="A16" s="1">
         <v>7</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>8</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="F17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>9</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="6">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>10</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="6">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>11</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="6">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
         <v>12</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="14"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
         <v>13</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="14"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
         <v>14</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
         <v>15</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H24" s="14"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>16</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H25" s="14"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="6">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>17</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H26" s="14"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="6">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>18</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H27" s="14"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>19</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="F28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="6">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>20</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="14"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="6">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>21</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="14"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="6">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>22</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="14"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="6">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>23</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="14"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="6">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>24</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="F33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="14"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="6">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>25</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="F34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H34" s="14"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="6">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>26</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="G35" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H35" s="14"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="6">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>27</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="F36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="14"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="6">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
         <v>28</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="F37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="14"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="6">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
         <v>29</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="F38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="14"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="6">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>30</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H39" s="14"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="6">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
         <v>31</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="F40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="14"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="6">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
         <v>32</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H41" s="14"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="6">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
         <v>33</v>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="6">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
         <v>34</v>
       </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-    </row>
-    <row r="65" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-    </row>
-    <row r="66" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-    </row>
-    <row r="67" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-    </row>
-    <row r="68" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-    </row>
-    <row r="69" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-    </row>
-    <row r="70" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-    </row>
-    <row r="71" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-    </row>
-    <row r="72" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-    </row>
-    <row r="73" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-    </row>
-    <row r="74" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-    </row>
-    <row r="75" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-    </row>
-    <row r="76" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-    </row>
-    <row r="77" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-    </row>
-    <row r="78" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-    </row>
-    <row r="79" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-    </row>
-    <row r="80" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-    </row>
-    <row r="81" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-    </row>
-    <row r="82" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-    </row>
-    <row r="83" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-    </row>
-    <row r="84" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-    </row>
-    <row r="85" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-    </row>
-    <row r="86" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-    </row>
-    <row r="87" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-    </row>
-    <row r="88" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
-    </row>
-    <row r="89" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="14"/>
-    </row>
-    <row r="90" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
-    </row>
-    <row r="91" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
-    </row>
-    <row r="92" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
-    </row>
-    <row r="93" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-    </row>
-    <row r="94" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="G94" s="14"/>
-      <c r="H94" s="14"/>
-    </row>
-    <row r="95" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="G95" s="14"/>
-      <c r="H95" s="14"/>
-    </row>
-    <row r="96" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="G96" s="14"/>
-      <c r="H96" s="14"/>
-    </row>
-    <row r="97" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
-      <c r="G97" s="14"/>
-      <c r="H97" s="14"/>
-    </row>
-    <row r="98" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="G98" s="14"/>
-      <c r="H98" s="14"/>
-    </row>
-    <row r="99" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
-      <c r="G99" s="14"/>
-      <c r="H99" s="14"/>
-    </row>
-    <row r="100" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="G100" s="14"/>
-      <c r="H100" s="14"/>
-    </row>
-    <row r="101" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D101" s="14"/>
-      <c r="E101" s="14"/>
-      <c r="G101" s="14"/>
-      <c r="H101" s="14"/>
-    </row>
-    <row r="102" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D102" s="14"/>
-      <c r="E102" s="14"/>
-      <c r="G102" s="14"/>
-      <c r="H102" s="14"/>
-    </row>
-    <row r="103" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D103" s="14"/>
-      <c r="E103" s="14"/>
-      <c r="G103" s="14"/>
-      <c r="H103" s="14"/>
-    </row>
-    <row r="104" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D104" s="14"/>
-      <c r="E104" s="14"/>
-      <c r="G104" s="14"/>
-      <c r="H104" s="14"/>
-    </row>
-    <row r="105" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D105" s="14"/>
-      <c r="E105" s="14"/>
-      <c r="G105" s="14"/>
-      <c r="H105" s="14"/>
-    </row>
-    <row r="106" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
-    </row>
-    <row r="107" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
-      <c r="G107" s="14"/>
-      <c r="H107" s="14"/>
-    </row>
-    <row r="108" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D108" s="14"/>
-      <c r="E108" s="14"/>
-      <c r="G108" s="14"/>
-      <c r="H108" s="14"/>
-    </row>
-    <row r="109" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="G109" s="14"/>
-      <c r="H109" s="14"/>
-    </row>
-    <row r="110" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D110" s="14"/>
-      <c r="E110" s="14"/>
-      <c r="G110" s="14"/>
-      <c r="H110" s="14"/>
-    </row>
-    <row r="111" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D111" s="14"/>
-      <c r="E111" s="14"/>
-      <c r="G111" s="14"/>
-      <c r="H111" s="14"/>
-    </row>
-    <row r="112" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D112" s="14"/>
-      <c r="E112" s="14"/>
-      <c r="G112" s="14"/>
-      <c r="H112" s="14"/>
-    </row>
-    <row r="113" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D113" s="14"/>
-      <c r="E113" s="14"/>
-      <c r="G113" s="14"/>
-      <c r="H113" s="14"/>
-    </row>
-    <row r="114" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D114" s="14"/>
-      <c r="E114" s="14"/>
-      <c r="G114" s="14"/>
-      <c r="H114" s="14"/>
-    </row>
-    <row r="115" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D115" s="14"/>
-      <c r="E115" s="14"/>
-      <c r="G115" s="14"/>
-      <c r="H115" s="14"/>
-    </row>
-    <row r="116" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D116" s="14"/>
-      <c r="E116" s="14"/>
-      <c r="G116" s="14"/>
-      <c r="H116" s="14"/>
-    </row>
-    <row r="117" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D117" s="14"/>
-      <c r="E117" s="14"/>
-      <c r="G117" s="14"/>
-      <c r="H117" s="14"/>
-    </row>
-    <row r="118" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D118" s="14"/>
-      <c r="E118" s="14"/>
-      <c r="G118" s="14"/>
-      <c r="H118" s="14"/>
-    </row>
-    <row r="119" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D119" s="14"/>
-      <c r="E119" s="14"/>
-      <c r="G119" s="14"/>
-      <c r="H119" s="14"/>
-    </row>
-    <row r="120" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D120" s="14"/>
-      <c r="E120" s="14"/>
-      <c r="G120" s="14"/>
-      <c r="H120" s="14"/>
-    </row>
-    <row r="121" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D121" s="14"/>
-      <c r="E121" s="14"/>
-      <c r="G121" s="14"/>
-      <c r="H121" s="14"/>
-    </row>
-    <row r="122" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D122" s="14"/>
-      <c r="E122" s="14"/>
-      <c r="G122" s="14"/>
-      <c r="H122" s="14"/>
-    </row>
-    <row r="123" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D123" s="14"/>
-      <c r="E123" s="14"/>
-      <c r="G123" s="14"/>
-      <c r="H123" s="14"/>
-    </row>
-    <row r="124" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D124" s="14"/>
-      <c r="E124" s="14"/>
-      <c r="G124" s="14"/>
-      <c r="H124" s="14"/>
-    </row>
-    <row r="125" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D125" s="14"/>
-      <c r="E125" s="14"/>
-      <c r="G125" s="14"/>
-      <c r="H125" s="14"/>
-    </row>
-    <row r="126" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D126" s="14"/>
-      <c r="E126" s="14"/>
-      <c r="G126" s="14"/>
-      <c r="H126" s="14"/>
-    </row>
-    <row r="127" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D127" s="14"/>
-      <c r="E127" s="14"/>
-      <c r="G127" s="14"/>
-      <c r="H127" s="14"/>
-    </row>
-    <row r="128" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D128" s="14"/>
-      <c r="E128" s="14"/>
-      <c r="G128" s="14"/>
-      <c r="H128" s="14"/>
-    </row>
-    <row r="129" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D129" s="14"/>
-      <c r="E129" s="14"/>
-      <c r="G129" s="14"/>
-      <c r="H129" s="14"/>
-    </row>
-    <row r="130" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D130" s="14"/>
-      <c r="E130" s="14"/>
-      <c r="G130" s="14"/>
-      <c r="H130" s="14"/>
-    </row>
-    <row r="131" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D131" s="14"/>
-      <c r="E131" s="14"/>
-      <c r="G131" s="14"/>
-      <c r="H131" s="14"/>
-    </row>
-    <row r="132" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D132" s="14"/>
-      <c r="E132" s="14"/>
-      <c r="G132" s="14"/>
-      <c r="H132" s="14"/>
-    </row>
-    <row r="133" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D133" s="14"/>
-      <c r="E133" s="14"/>
-      <c r="G133" s="14"/>
-      <c r="H133" s="14"/>
-    </row>
-    <row r="134" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D134" s="14"/>
-      <c r="E134" s="14"/>
-      <c r="G134" s="14"/>
-      <c r="H134" s="14"/>
-    </row>
-    <row r="135" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D135" s="14"/>
-      <c r="E135" s="14"/>
-      <c r="G135" s="14"/>
-      <c r="H135" s="14"/>
-    </row>
-    <row r="136" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D136" s="14"/>
-      <c r="E136" s="14"/>
-      <c r="G136" s="14"/>
-      <c r="H136" s="14"/>
-    </row>
-    <row r="137" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D137" s="14"/>
-      <c r="E137" s="14"/>
-      <c r="G137" s="14"/>
-      <c r="H137" s="14"/>
-    </row>
-    <row r="138" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D138" s="14"/>
-      <c r="E138" s="14"/>
-      <c r="G138" s="14"/>
-      <c r="H138" s="14"/>
-    </row>
-    <row r="139" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D139" s="14"/>
-      <c r="E139" s="14"/>
-      <c r="G139" s="14"/>
-      <c r="H139" s="14"/>
-    </row>
-    <row r="140" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D140" s="14"/>
-      <c r="E140" s="14"/>
-      <c r="G140" s="14"/>
-      <c r="H140" s="14"/>
-    </row>
-    <row r="141" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D141" s="14"/>
-      <c r="E141" s="14"/>
-      <c r="G141" s="14"/>
-      <c r="H141" s="14"/>
-    </row>
-    <row r="142" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D142" s="14"/>
-      <c r="E142" s="14"/>
-      <c r="G142" s="14"/>
-      <c r="H142" s="14"/>
-    </row>
-    <row r="143" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D143" s="14"/>
-      <c r="E143" s="14"/>
-      <c r="G143" s="14"/>
-      <c r="H143" s="14"/>
-    </row>
-    <row r="144" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D144" s="14"/>
-      <c r="E144" s="14"/>
-      <c r="G144" s="14"/>
-      <c r="H144" s="14"/>
-    </row>
-    <row r="145" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D145" s="14"/>
-      <c r="E145" s="14"/>
-      <c r="G145" s="14"/>
-      <c r="H145" s="14"/>
-    </row>
-    <row r="146" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D146" s="14"/>
-      <c r="E146" s="14"/>
-      <c r="G146" s="14"/>
-      <c r="H146" s="14"/>
-    </row>
-    <row r="147" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D147" s="14"/>
-      <c r="E147" s="14"/>
-      <c r="G147" s="14"/>
-      <c r="H147" s="14"/>
-    </row>
-    <row r="148" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D148" s="14"/>
-      <c r="E148" s="14"/>
-      <c r="G148" s="14"/>
-      <c r="H148" s="14"/>
-    </row>
-    <row r="149" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D149" s="14"/>
-      <c r="E149" s="14"/>
-      <c r="G149" s="14"/>
-      <c r="H149" s="14"/>
-    </row>
-    <row r="150" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D150" s="14"/>
-      <c r="E150" s="14"/>
-      <c r="G150" s="14"/>
-      <c r="H150" s="14"/>
-    </row>
-    <row r="151" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D151" s="14"/>
-      <c r="E151" s="14"/>
-      <c r="G151" s="14"/>
-      <c r="H151" s="14"/>
-    </row>
-    <row r="152" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D152" s="14"/>
-      <c r="E152" s="14"/>
-      <c r="G152" s="14"/>
-      <c r="H152" s="14"/>
-    </row>
-    <row r="153" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D153" s="14"/>
-      <c r="E153" s="14"/>
-      <c r="G153" s="14"/>
-      <c r="H153" s="14"/>
-    </row>
-    <row r="154" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D154" s="14"/>
-      <c r="E154" s="14"/>
-      <c r="G154" s="14"/>
-      <c r="H154" s="14"/>
-    </row>
-    <row r="155" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D155" s="14"/>
-      <c r="E155" s="14"/>
-      <c r="G155" s="14"/>
-      <c r="H155" s="14"/>
-    </row>
-    <row r="156" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D156" s="14"/>
-      <c r="E156" s="14"/>
-      <c r="G156" s="14"/>
-      <c r="H156" s="14"/>
-    </row>
-    <row r="157" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D157" s="14"/>
-      <c r="E157" s="14"/>
-      <c r="G157" s="14"/>
-      <c r="H157" s="14"/>
-    </row>
-    <row r="158" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D158" s="14"/>
-      <c r="E158" s="14"/>
-      <c r="G158" s="14"/>
-      <c r="H158" s="14"/>
-    </row>
-    <row r="159" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D159" s="14"/>
-      <c r="E159" s="14"/>
-      <c r="G159" s="14"/>
-      <c r="H159" s="14"/>
-    </row>
-    <row r="160" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D160" s="14"/>
-      <c r="E160" s="14"/>
-      <c r="G160" s="14"/>
-      <c r="H160" s="14"/>
-    </row>
-    <row r="161" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D161" s="14"/>
-      <c r="E161" s="14"/>
-      <c r="G161" s="14"/>
-      <c r="H161" s="14"/>
-    </row>
-    <row r="162" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D162" s="14"/>
-      <c r="E162" s="14"/>
-      <c r="G162" s="14"/>
-      <c r="H162" s="14"/>
-    </row>
-    <row r="163" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D163" s="14"/>
-      <c r="E163" s="14"/>
-      <c r="G163" s="14"/>
-      <c r="H163" s="14"/>
-    </row>
-    <row r="164" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D164" s="14"/>
-      <c r="E164" s="14"/>
-      <c r="G164" s="14"/>
-      <c r="H164" s="14"/>
-    </row>
-    <row r="165" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D165" s="14"/>
-      <c r="E165" s="14"/>
-      <c r="G165" s="14"/>
-      <c r="H165" s="14"/>
-    </row>
-    <row r="166" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D166" s="14"/>
-      <c r="E166" s="14"/>
-      <c r="G166" s="14"/>
-      <c r="H166" s="14"/>
-    </row>
-    <row r="167" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D167" s="14"/>
-      <c r="E167" s="14"/>
-      <c r="G167" s="14"/>
-      <c r="H167" s="14"/>
-    </row>
-    <row r="168" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D168" s="14"/>
-      <c r="E168" s="14"/>
-      <c r="G168" s="14"/>
-      <c r="H168" s="14"/>
-    </row>
-    <row r="169" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D169" s="14"/>
-      <c r="E169" s="14"/>
-      <c r="G169" s="14"/>
-      <c r="H169" s="14"/>
-    </row>
-    <row r="170" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D170" s="14"/>
-      <c r="E170" s="14"/>
-      <c r="G170" s="14"/>
-      <c r="H170" s="14"/>
-    </row>
-    <row r="171" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D171" s="14"/>
-      <c r="E171" s="14"/>
-      <c r="G171" s="14"/>
-      <c r="H171" s="14"/>
-    </row>
-    <row r="172" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D172" s="14"/>
-      <c r="E172" s="14"/>
-      <c r="G172" s="14"/>
-      <c r="H172" s="14"/>
-    </row>
-    <row r="173" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D173" s="14"/>
-      <c r="E173" s="14"/>
-      <c r="G173" s="14"/>
-      <c r="H173" s="14"/>
-    </row>
-    <row r="174" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D174" s="14"/>
-      <c r="E174" s="14"/>
-      <c r="G174" s="14"/>
-      <c r="H174" s="14"/>
-    </row>
-    <row r="175" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D175" s="14"/>
-      <c r="E175" s="14"/>
-      <c r="G175" s="14"/>
-      <c r="H175" s="14"/>
-    </row>
-    <row r="176" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D176" s="14"/>
-      <c r="E176" s="14"/>
-      <c r="G176" s="14"/>
-      <c r="H176" s="14"/>
-    </row>
-    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D177" s="14"/>
-      <c r="E177" s="14"/>
-      <c r="G177" s="14"/>
-      <c r="H177" s="14"/>
-    </row>
-    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D178" s="14"/>
-      <c r="E178" s="14"/>
-      <c r="G178" s="14"/>
-      <c r="H178" s="14"/>
-    </row>
-    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D179" s="14"/>
-      <c r="E179" s="14"/>
-      <c r="G179" s="14"/>
-      <c r="H179" s="14"/>
-    </row>
-    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D180" s="14"/>
-      <c r="E180" s="14"/>
-      <c r="G180" s="14"/>
-      <c r="H180" s="14"/>
-    </row>
-    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D181" s="14"/>
-      <c r="E181" s="14"/>
-      <c r="G181" s="14"/>
-      <c r="H181" s="14"/>
-    </row>
-    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D182" s="14"/>
-      <c r="E182" s="14"/>
-      <c r="G182" s="14"/>
-      <c r="H182" s="14"/>
-    </row>
-    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D183" s="14"/>
-      <c r="E183" s="14"/>
-      <c r="G183" s="14"/>
-      <c r="H183" s="14"/>
-    </row>
-    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D184" s="14"/>
-      <c r="E184" s="14"/>
-      <c r="G184" s="14"/>
-      <c r="H184" s="14"/>
-    </row>
-    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D185" s="14"/>
-      <c r="E185" s="14"/>
-      <c r="G185" s="14"/>
-      <c r="H185" s="14"/>
-    </row>
-    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D186" s="14"/>
-      <c r="E186" s="14"/>
-      <c r="G186" s="14"/>
-      <c r="H186" s="14"/>
-    </row>
-    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D187" s="14"/>
-      <c r="E187" s="14"/>
-      <c r="G187" s="14"/>
-      <c r="H187" s="14"/>
-    </row>
-    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D188" s="14"/>
-      <c r="E188" s="14"/>
-      <c r="G188" s="14"/>
-      <c r="H188" s="14"/>
-    </row>
-    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D189" s="14"/>
-      <c r="E189" s="14"/>
-      <c r="G189" s="14"/>
-      <c r="H189" s="14"/>
-    </row>
-    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D190" s="14"/>
-      <c r="E190" s="14"/>
-      <c r="G190" s="14"/>
-      <c r="H190" s="14"/>
-    </row>
-    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D191" s="14"/>
-      <c r="E191" s="14"/>
-      <c r="G191" s="14"/>
-      <c r="H191" s="14"/>
-    </row>
-    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D192" s="14"/>
-      <c r="E192" s="14"/>
-      <c r="G192" s="14"/>
-      <c r="H192" s="14"/>
-    </row>
-    <row r="193" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D193" s="14"/>
-      <c r="E193" s="14"/>
-      <c r="G193" s="14"/>
-      <c r="H193" s="14"/>
-    </row>
-    <row r="194" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D194" s="14"/>
-      <c r="E194" s="14"/>
-      <c r="G194" s="14"/>
-      <c r="H194" s="14"/>
-    </row>
-    <row r="195" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D195" s="14"/>
-      <c r="E195" s="14"/>
-      <c r="G195" s="14"/>
-      <c r="H195" s="14"/>
-    </row>
-    <row r="196" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D196" s="14"/>
-      <c r="E196" s="14"/>
-      <c r="G196" s="14"/>
-      <c r="H196" s="14"/>
-    </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D197" s="14"/>
-      <c r="E197" s="14"/>
-      <c r="G197" s="14"/>
-      <c r="H197" s="14"/>
-    </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D198" s="14"/>
-      <c r="E198" s="14"/>
-      <c r="G198" s="14"/>
-      <c r="H198" s="14"/>
-    </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D199" s="14"/>
-      <c r="E199" s="14"/>
-      <c r="G199" s="14"/>
-      <c r="H199" s="14"/>
-    </row>
-    <row r="200" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D200" s="14"/>
-      <c r="E200" s="14"/>
-      <c r="G200" s="14"/>
-      <c r="H200" s="14"/>
-    </row>
-    <row r="201" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D201" s="14"/>
-    </row>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2"/>
+    <row r="49" x14ac:dyDescent="0.2"/>
+    <row r="50" x14ac:dyDescent="0.2"/>
+    <row r="51" x14ac:dyDescent="0.2"/>
+    <row r="52" x14ac:dyDescent="0.2"/>
+    <row r="53" x14ac:dyDescent="0.2"/>
+    <row r="54" x14ac:dyDescent="0.2"/>
+    <row r="55" x14ac:dyDescent="0.2"/>
+    <row r="56" x14ac:dyDescent="0.2"/>
+    <row r="57" x14ac:dyDescent="0.2"/>
+    <row r="58" x14ac:dyDescent="0.2"/>
+    <row r="59" x14ac:dyDescent="0.2"/>
+    <row r="60" x14ac:dyDescent="0.2"/>
+    <row r="61" x14ac:dyDescent="0.2"/>
+    <row r="62" x14ac:dyDescent="0.2"/>
+    <row r="63" x14ac:dyDescent="0.2"/>
+    <row r="64" x14ac:dyDescent="0.2"/>
+    <row r="65" x14ac:dyDescent="0.2"/>
+    <row r="66" x14ac:dyDescent="0.2"/>
+    <row r="67" x14ac:dyDescent="0.2"/>
+    <row r="68" x14ac:dyDescent="0.2"/>
+    <row r="69" x14ac:dyDescent="0.2"/>
+    <row r="70" x14ac:dyDescent="0.2"/>
+    <row r="71" x14ac:dyDescent="0.2"/>
+    <row r="72" x14ac:dyDescent="0.2"/>
+    <row r="73" x14ac:dyDescent="0.2"/>
+    <row r="74" x14ac:dyDescent="0.2"/>
+    <row r="75" x14ac:dyDescent="0.2"/>
+    <row r="76" x14ac:dyDescent="0.2"/>
+    <row r="77" x14ac:dyDescent="0.2"/>
+    <row r="78" x14ac:dyDescent="0.2"/>
+    <row r="79" x14ac:dyDescent="0.2"/>
+    <row r="80" x14ac:dyDescent="0.2"/>
+    <row r="81" x14ac:dyDescent="0.2"/>
+    <row r="82" x14ac:dyDescent="0.2"/>
+    <row r="83" x14ac:dyDescent="0.2"/>
+    <row r="84" x14ac:dyDescent="0.2"/>
+    <row r="85" x14ac:dyDescent="0.2"/>
+    <row r="86" x14ac:dyDescent="0.2"/>
+    <row r="87" x14ac:dyDescent="0.2"/>
+    <row r="88" x14ac:dyDescent="0.2"/>
+    <row r="89" x14ac:dyDescent="0.2"/>
+    <row r="90" x14ac:dyDescent="0.2"/>
+    <row r="91" x14ac:dyDescent="0.2"/>
+    <row r="92" x14ac:dyDescent="0.2"/>
+    <row r="93" x14ac:dyDescent="0.2"/>
+    <row r="94" x14ac:dyDescent="0.2"/>
+    <row r="95" x14ac:dyDescent="0.2"/>
+    <row r="96" x14ac:dyDescent="0.2"/>
+    <row r="97" x14ac:dyDescent="0.2"/>
+    <row r="98" x14ac:dyDescent="0.2"/>
+    <row r="99" x14ac:dyDescent="0.2"/>
+    <row r="100" x14ac:dyDescent="0.2"/>
+    <row r="101" x14ac:dyDescent="0.2"/>
+    <row r="102" x14ac:dyDescent="0.2"/>
+    <row r="103" x14ac:dyDescent="0.2"/>
+    <row r="104" x14ac:dyDescent="0.2"/>
+    <row r="105" x14ac:dyDescent="0.2"/>
+    <row r="106" x14ac:dyDescent="0.2"/>
+    <row r="107" x14ac:dyDescent="0.2"/>
+    <row r="108" x14ac:dyDescent="0.2"/>
+    <row r="109" x14ac:dyDescent="0.2"/>
+    <row r="110" x14ac:dyDescent="0.2"/>
+    <row r="111" x14ac:dyDescent="0.2"/>
+    <row r="112" x14ac:dyDescent="0.2"/>
+    <row r="113" x14ac:dyDescent="0.2"/>
+    <row r="114" x14ac:dyDescent="0.2"/>
+    <row r="115" x14ac:dyDescent="0.2"/>
+    <row r="116" x14ac:dyDescent="0.2"/>
+    <row r="117" x14ac:dyDescent="0.2"/>
+    <row r="118" x14ac:dyDescent="0.2"/>
+    <row r="119" x14ac:dyDescent="0.2"/>
+    <row r="120" x14ac:dyDescent="0.2"/>
+    <row r="121" x14ac:dyDescent="0.2"/>
+    <row r="122" x14ac:dyDescent="0.2"/>
+    <row r="123" x14ac:dyDescent="0.2"/>
+    <row r="124" x14ac:dyDescent="0.2"/>
+    <row r="125" x14ac:dyDescent="0.2"/>
+    <row r="126" x14ac:dyDescent="0.2"/>
+    <row r="127" x14ac:dyDescent="0.2"/>
+    <row r="128" x14ac:dyDescent="0.2"/>
+    <row r="129" x14ac:dyDescent="0.2"/>
+    <row r="130" x14ac:dyDescent="0.2"/>
+    <row r="131" x14ac:dyDescent="0.2"/>
+    <row r="132" x14ac:dyDescent="0.2"/>
+    <row r="133" x14ac:dyDescent="0.2"/>
+    <row r="134" x14ac:dyDescent="0.2"/>
+    <row r="135" x14ac:dyDescent="0.2"/>
+    <row r="136" x14ac:dyDescent="0.2"/>
+    <row r="137" x14ac:dyDescent="0.2"/>
+    <row r="138" x14ac:dyDescent="0.2"/>
+    <row r="139" x14ac:dyDescent="0.2"/>
+    <row r="140" x14ac:dyDescent="0.2"/>
+    <row r="141" x14ac:dyDescent="0.2"/>
+    <row r="142" x14ac:dyDescent="0.2"/>
+    <row r="143" x14ac:dyDescent="0.2"/>
+    <row r="144" x14ac:dyDescent="0.2"/>
+    <row r="145" x14ac:dyDescent="0.2"/>
+    <row r="146" x14ac:dyDescent="0.2"/>
+    <row r="147" x14ac:dyDescent="0.2"/>
+    <row r="148" x14ac:dyDescent="0.2"/>
+    <row r="149" x14ac:dyDescent="0.2"/>
+    <row r="150" x14ac:dyDescent="0.2"/>
+    <row r="151" x14ac:dyDescent="0.2"/>
+    <row r="152" x14ac:dyDescent="0.2"/>
+    <row r="153" x14ac:dyDescent="0.2"/>
+    <row r="154" x14ac:dyDescent="0.2"/>
+    <row r="155" x14ac:dyDescent="0.2"/>
+    <row r="156" x14ac:dyDescent="0.2"/>
+    <row r="157" x14ac:dyDescent="0.2"/>
+    <row r="158" x14ac:dyDescent="0.2"/>
+    <row r="159" x14ac:dyDescent="0.2"/>
+    <row r="160" x14ac:dyDescent="0.2"/>
+    <row r="161" x14ac:dyDescent="0.2"/>
+    <row r="162" x14ac:dyDescent="0.2"/>
+    <row r="163" x14ac:dyDescent="0.2"/>
+    <row r="164" x14ac:dyDescent="0.2"/>
+    <row r="165" x14ac:dyDescent="0.2"/>
+    <row r="166" x14ac:dyDescent="0.2"/>
+    <row r="167" x14ac:dyDescent="0.2"/>
+    <row r="168" x14ac:dyDescent="0.2"/>
+    <row r="169" x14ac:dyDescent="0.2"/>
+    <row r="170" x14ac:dyDescent="0.2"/>
+    <row r="171" x14ac:dyDescent="0.2"/>
+    <row r="172" x14ac:dyDescent="0.2"/>
+    <row r="173" x14ac:dyDescent="0.2"/>
+    <row r="174" x14ac:dyDescent="0.2"/>
+    <row r="175" x14ac:dyDescent="0.2"/>
+    <row r="176" x14ac:dyDescent="0.2"/>
+    <row r="177" x14ac:dyDescent="0.2"/>
+    <row r="178" x14ac:dyDescent="0.2"/>
+    <row r="179" x14ac:dyDescent="0.2"/>
+    <row r="180" x14ac:dyDescent="0.2"/>
+    <row r="181" x14ac:dyDescent="0.2"/>
+    <row r="182" x14ac:dyDescent="0.2"/>
+    <row r="183" x14ac:dyDescent="0.2"/>
+    <row r="184" x14ac:dyDescent="0.2"/>
+    <row r="185" x14ac:dyDescent="0.2"/>
+    <row r="186" x14ac:dyDescent="0.2"/>
+    <row r="187" x14ac:dyDescent="0.2"/>
+    <row r="188" x14ac:dyDescent="0.2"/>
+    <row r="189" x14ac:dyDescent="0.2"/>
+    <row r="190" x14ac:dyDescent="0.2"/>
+    <row r="191" x14ac:dyDescent="0.2"/>
+    <row r="192" x14ac:dyDescent="0.2"/>
+    <row r="193" x14ac:dyDescent="0.2"/>
+    <row r="194" x14ac:dyDescent="0.2"/>
+    <row r="195" x14ac:dyDescent="0.2"/>
+    <row r="196" x14ac:dyDescent="0.2"/>
+    <row r="197" x14ac:dyDescent="0.2"/>
+    <row r="198" x14ac:dyDescent="0.2"/>
+    <row r="199" x14ac:dyDescent="0.2"/>
+    <row r="200" x14ac:dyDescent="0.2"/>
+    <row r="201" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
@@ -2696,20 +1898,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
@@ -2717,7 +1919,7 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
@@ -2725,7 +1927,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -2733,7 +1935,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="10" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
@@ -2741,7 +1943,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
@@ -2749,7 +1951,7 @@
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
@@ -2757,7 +1959,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
@@ -2765,7 +1967,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
@@ -2773,7 +1975,7 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
@@ -2781,7 +1983,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
@@ -2789,7 +1991,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
@@ -2797,7 +1999,7 @@
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="s">
@@ -2805,20 +2007,20 @@
       </c>
     </row>
     <row r="21" spans="2:3" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C23" t="s">
@@ -2826,7 +2028,7 @@
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
@@ -2834,7 +2036,7 @@
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="11" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
@@ -2842,7 +2044,7 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="11" t="s">
         <v>46</v>
       </c>
       <c r="C26" t="s">
@@ -2850,7 +2052,7 @@
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
@@ -2858,7 +2060,7 @@
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C28" t="s">
@@ -2866,7 +2068,7 @@
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C29" t="s">
@@ -2874,7 +2076,7 @@
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C30" t="s">
@@ -2882,7 +2084,7 @@
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="11" t="s">
         <v>56</v>
       </c>
       <c r="C31" t="s">
@@ -2890,7 +2092,7 @@
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C32" t="s">
@@ -2898,7 +2100,7 @@
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C33" t="s">
@@ -2906,7 +2108,7 @@
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C34" t="s">
@@ -2914,7 +2116,7 @@
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="11" t="s">
         <v>64</v>
       </c>
       <c r="C35" t="s">
@@ -2922,7 +2124,7 @@
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C36" t="s">
@@ -2930,7 +2132,7 @@
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C37" t="s">
@@ -2938,7 +2140,7 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="C38" t="s">

--- a/Project Requirements Form (Excel).xlsx
+++ b/Project Requirements Form (Excel).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parke\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parke\OneDrive\Documents\GitHub\CodeTogether\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2E9DFFC-821E-4C6E-827A-C75BB8035C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F21791-C141-4848-9470-0C6C861ED7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Requirements" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="141">
   <si>
     <t>CSCE 40003 Software Engineering</t>
   </si>
@@ -407,6 +407,48 @@
   </si>
   <si>
     <t>accurate forcasting</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>button works/ search works</t>
+  </si>
+  <si>
+    <t>launch</t>
+  </si>
+  <si>
+    <t>user can see,use and update home page</t>
+  </si>
+  <si>
+    <t>adding/removing music, playable, and audio works</t>
+  </si>
+  <si>
+    <t>enhanced experience at latest</t>
+  </si>
+  <si>
+    <t>list info for users to have an easier usage of functionality</t>
+  </si>
+  <si>
+    <t>pg can be viewed and update by users</t>
+  </si>
+  <si>
+    <t>user can see tips/frequently asked questions</t>
+  </si>
+  <si>
+    <t>user can use button to contact us</t>
+  </si>
+  <si>
+    <t>users can view and understand privacy policy page</t>
+  </si>
+  <si>
+    <t>visiable accurate date/time display</t>
+  </si>
+  <si>
+    <t>bday msg appears on appropriate day of users bday</t>
+  </si>
+  <si>
+    <t>messages appear and work correctly</t>
   </si>
 </sst>
 </file>
@@ -541,7 +583,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -579,6 +621,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1067,6 +1112,9 @@
       <c r="G11" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="H11" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -1090,6 +1138,15 @@
       <c r="G12" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="H12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -1113,6 +1170,9 @@
       <c r="G13" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="H13" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -1136,6 +1196,15 @@
       <c r="G14" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="H14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -1177,7 +1246,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>8</v>
       </c>
@@ -1199,8 +1268,17 @@
       <c r="G17" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>9</v>
       </c>
@@ -1220,7 +1298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>10</v>
       </c>
@@ -1237,7 +1315,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>11</v>
       </c>
@@ -1254,7 +1332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>12</v>
       </c>
@@ -1274,7 +1352,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>13</v>
       </c>
@@ -1294,7 +1372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>14</v>
       </c>
@@ -1311,7 +1389,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>15</v>
       </c>
@@ -1328,7 +1406,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>16</v>
       </c>
@@ -1345,7 +1423,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>17</v>
       </c>
@@ -1367,8 +1445,17 @@
       <c r="G26" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>18</v>
       </c>
@@ -1388,7 +1475,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>19</v>
       </c>
@@ -1407,8 +1494,17 @@
       <c r="G28" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20</v>
       </c>
@@ -1425,7 +1521,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>21</v>
       </c>
@@ -1442,7 +1538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>22</v>
       </c>
@@ -1459,7 +1555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>23</v>
       </c>
@@ -1478,8 +1574,17 @@
       <c r="G32" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>24</v>
       </c>
@@ -1498,8 +1603,17 @@
       <c r="G33" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>25</v>
       </c>
@@ -1518,8 +1632,17 @@
       <c r="G34" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>26</v>
       </c>
@@ -1536,7 +1659,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>27</v>
       </c>
@@ -1555,8 +1678,17 @@
       <c r="G36" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>28</v>
       </c>
@@ -1578,8 +1710,17 @@
       <c r="G37" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>29</v>
       </c>
@@ -1598,8 +1739,17 @@
       <c r="G38" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>30</v>
       </c>
@@ -1616,7 +1766,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>31</v>
       </c>
@@ -1636,7 +1786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>32</v>
       </c>
@@ -1653,21 +1803,21 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2"/>
     <row r="49" x14ac:dyDescent="0.2"/>
     <row r="50" x14ac:dyDescent="0.2"/>
     <row r="51" x14ac:dyDescent="0.2"/>

--- a/Project Requirements Form (Excel).xlsx
+++ b/Project Requirements Form (Excel).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parke\OneDrive\Documents\GitHub\CodeTogether\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F21791-C141-4848-9470-0C6C861ED7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F51F6E-7FD3-4456-B712-BC399266C086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="143">
   <si>
     <t>CSCE 40003 Software Engineering</t>
   </si>
@@ -449,6 +449,12 @@
   </si>
   <si>
     <t>messages appear and work correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">displays weather accuratly for user </t>
+  </si>
+  <si>
+    <t>enhanced experience</t>
   </si>
 </sst>
 </file>
@@ -607,6 +613,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -621,9 +630,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -913,32 +919,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
@@ -962,11 +968,11 @@
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4"/>
@@ -982,11 +988,11 @@
       <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5"/>
@@ -1017,20 +1023,20 @@
       <c r="J7"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -1274,7 +1280,7 @@
       <c r="I17" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" s="13" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1784,6 +1790,12 @@
       </c>
       <c r="G40" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
